--- a/data/trans_dic/IP04D$notiene-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -612,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -675,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 25,5</t>
+          <t>9,17; 25,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,53; 51,49</t>
+          <t>29,67; 50,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,93; 58,96</t>
+          <t>31,36; 59,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,95; 29,79</t>
+          <t>12,53; 29,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,46; 61,75</t>
+          <t>41,48; 61,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,66; 35,67</t>
+          <t>16,18; 35,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,0; 25,11</t>
+          <t>13,14; 25,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,06; 53,28</t>
+          <t>38,53; 53,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,51; 42,55</t>
+          <t>26,03; 43,46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -785,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 15,0</t>
+          <t>4,69; 14,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,28; 29,14</t>
+          <t>16,18; 29,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 10,09</t>
+          <t>1,81; 10,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 13,37</t>
+          <t>3,86; 12,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,51; 34,84</t>
+          <t>21,28; 34,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 16,88</t>
+          <t>6,2; 16,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 11,63</t>
+          <t>5,25; 11,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,96; 30,3</t>
+          <t>20,4; 30,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 12,24</t>
+          <t>4,91; 12,07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -895,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,79</t>
+          <t>0,0; 5,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,48</t>
+          <t>1,04; 9,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,12</t>
+          <t>0,0; 7,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,7</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -920,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 7,31</t>
+          <t>0,58; 7,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,56</t>
+          <t>0,54; 5,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 5,56</t>
+          <t>0,74; 5,35</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,67</t>
+          <t>0,82; 7,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 7,44</t>
+          <t>0,73; 7,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,67</t>
+          <t>0,0; 9,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 13,79</t>
+          <t>2,96; 13,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 10,77</t>
+          <t>0,68; 10,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,57</t>
+          <t>0,39; 3,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 9,05</t>
+          <t>2,5; 9,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 7,23</t>
+          <t>1,02; 7,65</t>
         </is>
       </c>
     </row>
@@ -1115,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,69</t>
+          <t>1,62; 14,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,29</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,61</t>
+          <t>1,46; 13,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,85</t>
+          <t>1,89; 10,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,35</t>
+          <t>0,0; 3,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1225,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,57; 36,84</t>
+          <t>16,94; 37,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 9,79</t>
+          <t>1,11; 9,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,55; 36,04</t>
+          <t>16,69; 36,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,23; 35,07</t>
+          <t>19,98; 34,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,07</t>
+          <t>0,53; 5,15</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1335,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,1</t>
+          <t>0,48; 4,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,29; 25,61</t>
+          <t>14,31; 25,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,1; 41,79</t>
+          <t>27,16; 41,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,16</t>
+          <t>1,09; 5,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,84; 22,56</t>
+          <t>11,78; 22,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,52; 51,27</t>
+          <t>33,4; 50,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,21</t>
+          <t>1,13; 4,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,31; 21,87</t>
+          <t>14,51; 21,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,01; 45,08</t>
+          <t>32,71; 44,7</t>
         </is>
       </c>
     </row>
@@ -1445,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,53</t>
+          <t>0,81; 4,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,96</t>
+          <t>0,97; 5,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,2</t>
+          <t>0,36; 3,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,25</t>
+          <t>0,37; 3,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,24</t>
+          <t>0,46; 4,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,22</t>
+          <t>0,79; 3,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,93</t>
+          <t>0,2; 1,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,87</t>
+          <t>1,06; 4,06</t>
         </is>
       </c>
     </row>
@@ -1560,42 +1563,42 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,14; 15,27</t>
+          <t>11,16; 15,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,82; 16,72</t>
+          <t>10,97; 16,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,5</t>
+          <t>2,97; 5,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,81; 17,53</t>
+          <t>12,95; 17,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,4; 16,98</t>
+          <t>11,33; 17,15</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,0</t>
+          <t>3,28; 5,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,53; 15,66</t>
+          <t>12,66; 15,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,98; 16,04</t>
+          <t>11,79; 16,12</t>
         </is>
       </c>
     </row>
@@ -1624,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9164</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22896</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>31615</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13027</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33408</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19797</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>22192</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>56303</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>51411</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5180; 14289</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17019; 28897</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22985; 43252</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8120; 19433</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>26739; 39844</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>12840; 28486</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15938; 30831</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>46939; 64712</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>39735; 66333</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8906</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23095</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6469</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8260</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30568</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13336</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17166</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>53663</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>19805</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4882; 15380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>16824; 30683</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2317; 13081</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4246; 13381</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>23473; 38574</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7909; 21336</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11241; 24957</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>43712; 66071</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>12542; 30803</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2289</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1697</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1446</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2959</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3085</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4074</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>697; 6252</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4524</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3578</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3368</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>386; 5198</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5039</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>733; 7008</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>928; 6716</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1947</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6041</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2929</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7988</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4544</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>640; 5482</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>558; 5956</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6304</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2404; 11041</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>533; 8322</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>630; 5539</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3938; 14628</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1497; 11264</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2246</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4657</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>709; 6501</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3503</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>685; 6258</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1712; 9566</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2992</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>14132</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>15275</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>29406</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2263</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9193; 20131</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>512; 4541</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>9636; 21124</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2572</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>22377; 38538</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>542; 5269</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>26465</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>43241</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4184</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>23280</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>64706</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>6434</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>49745</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>107947</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>664; 6092</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>19551; 34752</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>33822; 52021</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1593; 8619</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>16475; 31010</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>51793; 78839</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3212; 11477</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>40110; 59440</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>91450; 124964</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3355</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2530</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>5459</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2586</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>6192</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1321; 7022</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2847</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1272; 7662</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>625; 6490</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>626; 5597</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>719; 6980</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2662; 10169</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>674; 6591</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>3061; 11680</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>28922</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>91985</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>89694</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>30537</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>111264</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>105554</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>59459</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>203248</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>195248</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>21329; 39146</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>78140; 107958</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>72945; 110824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>22306; 41019</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>95798; 131128</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>86163; 130400</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>47894; 74764</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>182313; 228599</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>168093; 229820</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$notiene-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 25,31</t>
+          <t>9,51; 24,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,67; 50,37</t>
+          <t>30,14; 52,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,36; 59,02</t>
+          <t>31,56; 58,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,53; 29,99</t>
+          <t>12,88; 30,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,48; 61,81</t>
+          <t>42,47; 62,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,18; 35,89</t>
+          <t>16,84; 35,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,14; 25,42</t>
+          <t>12,88; 24,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,53; 53,12</t>
+          <t>39,16; 53,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,03; 43,46</t>
+          <t>25,8; 43,89</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 14,78</t>
+          <t>4,7; 14,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,18; 29,52</t>
+          <t>16,47; 29,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 10,25</t>
+          <t>1,83; 10,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 12,18</t>
+          <t>3,92; 12,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,28; 34,98</t>
+          <t>21,2; 34,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 16,72</t>
+          <t>5,96; 16,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 11,66</t>
+          <t>5,1; 11,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,4; 30,84</t>
+          <t>20,55; 30,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 12,07</t>
+          <t>4,69; 11,8</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,98</t>
+          <t>0,0; 5,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,35</t>
+          <t>1,03; 9,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 8,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>0,0; 4,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 7,74</t>
+          <t>0,56; 7,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,61</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,13</t>
+          <t>0,56; 5,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 5,35</t>
+          <t>0,91; 5,69</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,05</t>
+          <t>0,8; 7,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,82</t>
+          <t>0,73; 7,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,12</t>
+          <t>0,0; 9,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,27 +1028,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 13,6</t>
+          <t>3,06; 14,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 10,65</t>
+          <t>0,71; 12,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,46</t>
+          <t>0,39; 3,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 9,3</t>
+          <t>2,56; 9,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 7,65</t>
+          <t>1,01; 7,25</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,81</t>
+          <t>1,62; 14,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 7,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,39</t>
+          <t>1,46; 13,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 10,55</t>
+          <t>1,79; 9,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,94; 37,09</t>
+          <t>18,06; 36,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,84</t>
+          <t>1,09; 12,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,69; 36,59</t>
+          <t>17,08; 37,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 7,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,98; 34,41</t>
+          <t>19,69; 33,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,15</t>
+          <t>0,55; 5,15</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,39</t>
+          <t>0,47; 4,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,31; 25,44</t>
+          <t>14,72; 25,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,16; 41,78</t>
+          <t>28,23; 42,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,91</t>
+          <t>1,3; 5,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,78; 22,16</t>
+          <t>12,04; 21,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,4; 50,84</t>
+          <t>32,14; 50,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,03</t>
+          <t>1,15; 4,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,51; 21,5</t>
+          <t>14,3; 22,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32,71; 44,7</t>
+          <t>33,22; 44,85</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,28</t>
+          <t>0,75; 5,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1458,37 +1458,37 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,82</t>
+          <t>1,16; 6,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,79</t>
+          <t>0,36; 3,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,29</t>
+          <t>0,37; 3,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,47</t>
+          <t>0,46; 4,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,03</t>
+          <t>0,79; 3,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,97</t>
+          <t>0,22; 1,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,06</t>
+          <t>1,1; 4,26</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,53</t>
+          <t>2,93; 5,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,16; 15,42</t>
+          <t>11,36; 15,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,97; 16,66</t>
+          <t>10,8; 16,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,45</t>
+          <t>2,95; 5,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,95; 17,72</t>
+          <t>12,99; 17,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,33; 17,15</t>
+          <t>11,3; 16,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,12</t>
+          <t>3,22; 4,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,66; 15,87</t>
+          <t>12,6; 15,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,79; 16,12</t>
+          <t>11,83; 16,04</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5180; 14289</t>
+          <t>5371; 13814</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17019; 28897</t>
+          <t>17293; 29836</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22985; 43252</t>
+          <t>23126; 43138</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8120; 19433</t>
+          <t>8349; 19745</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26739; 39844</t>
+          <t>27380; 40269</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12840; 28486</t>
+          <t>13362; 28102</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15938; 30831</t>
+          <t>15617; 29931</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46939; 64712</t>
+          <t>47715; 64796</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39735; 66333</t>
+          <t>39382; 66996</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4882; 15380</t>
+          <t>4891; 15181</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16824; 30683</t>
+          <t>17118; 30953</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2317; 13081</t>
+          <t>2334; 12989</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4246; 13381</t>
+          <t>4307; 13740</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23473; 38574</t>
+          <t>23377; 37771</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7909; 21336</t>
+          <t>7610; 21425</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11241; 24957</t>
+          <t>10920; 25144</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43712; 66071</t>
+          <t>44020; 64427</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12542; 30803</t>
+          <t>11962; 30115</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4074</t>
+          <t>0; 3641</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>697; 6252</t>
+          <t>686; 6452</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4524</t>
+          <t>0; 4849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3578</t>
+          <t>0; 3218</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3368</t>
+          <t>0; 3354</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>386; 5198</t>
+          <t>376; 5007</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5039</t>
+          <t>0; 5064</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>733; 7008</t>
+          <t>767; 7111</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>928; 6716</t>
+          <t>1142; 7136</t>
         </is>
       </c>
     </row>
@@ -2350,17 +2350,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>640; 5482</t>
+          <t>619; 5765</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>558; 5956</t>
+          <t>554; 5334</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6304</t>
+          <t>0; 6646</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2370,27 +2370,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2404; 11041</t>
+          <t>2481; 11914</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>533; 8322</t>
+          <t>551; 10093</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>630; 5539</t>
+          <t>631; 5562</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3938; 14628</t>
+          <t>4020; 14239</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1497; 11264</t>
+          <t>1493; 10677</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>709; 6501</t>
+          <t>711; 6268</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3503</t>
+          <t>0; 3035</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>685; 6258</t>
+          <t>684; 6208</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1712; 9566</t>
+          <t>1627; 9051</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2992</t>
+          <t>0; 2979</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9193; 20131</t>
+          <t>9802; 20023</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>512; 4541</t>
+          <t>505; 5556</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9636; 21124</t>
+          <t>9863; 21543</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2572</t>
+          <t>0; 4471</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22377; 38538</t>
+          <t>22057; 37608</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>542; 5269</t>
+          <t>562; 5275</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>664; 6092</t>
+          <t>651; 6005</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19551; 34752</t>
+          <t>20115; 34732</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33822; 52021</t>
+          <t>35147; 53322</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1593; 8619</t>
+          <t>1899; 8732</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16475; 31010</t>
+          <t>16850; 30736</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>51793; 78839</t>
+          <t>49832; 78732</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3212; 11477</t>
+          <t>3273; 11490</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>40110; 59440</t>
+          <t>39540; 61324</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>91450; 124964</t>
+          <t>92867; 125380</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1321; 7022</t>
+          <t>1223; 8325</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2847</t>
+          <t>0; 2848</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1272; 7662</t>
+          <t>1525; 8008</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>625; 6490</t>
+          <t>623; 5695</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>626; 5597</t>
+          <t>625; 5540</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>719; 6980</t>
+          <t>724; 7013</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2662; 10169</t>
+          <t>2637; 10504</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>674; 6591</t>
+          <t>728; 6486</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3061; 11680</t>
+          <t>3170; 12251</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>21329; 39146</t>
+          <t>20748; 37967</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>78140; 107958</t>
+          <t>79563; 105936</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>72945; 110824</t>
+          <t>71831; 111837</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22306; 41019</t>
+          <t>22184; 42082</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>95798; 131128</t>
+          <t>96101; 128502</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86163; 130400</t>
+          <t>85913; 128326</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47894; 74764</t>
+          <t>47059; 72732</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>182313; 228599</t>
+          <t>181435; 227202</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>168093; 229820</t>
+          <t>168616; 228630</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$notiene-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Provincia-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de calefacción en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20,1%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51,83%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>16,23%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>39,91%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>43,14%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20,1%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>51,83%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,51; 24,47</t>
+          <t>11,95; 29,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,14; 52,0</t>
+          <t>41,46; 61,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,56; 58,87</t>
+          <t>14,7; 30,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,88; 30,47</t>
+          <t>9,59; 25,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,47; 62,47</t>
+          <t>30,53; 51,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,84; 35,41</t>
+          <t>22,95; 42,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,88; 24,68</t>
+          <t>13,0; 25,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,16; 53,18</t>
+          <t>39,06; 53,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,8; 43,89</t>
+          <t>20,3; 32,8</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,52%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27,72%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>8,56%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>22,22%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>27,72%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,7; 14,59</t>
+          <t>4,04; 13,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,47; 29,78</t>
+          <t>21,51; 34,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 10,18</t>
+          <t>6,01; 17,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 12,5</t>
+          <t>4,39; 15,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,2; 34,25</t>
+          <t>16,28; 29,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 16,79</t>
+          <t>2,81; 10,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,1; 11,75</t>
+          <t>4,99; 11,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,55; 30,07</t>
+          <t>20,96; 30,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 11,8</t>
+          <t>5,47; 12,35</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,42%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,34</t>
+          <t>0,0; 5,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,65</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,32</t>
+          <t>0,52; 7,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,52</t>
+          <t>0,0; 5,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>1,04; 9,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 7,46</t>
+          <t>0,0; 7,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,2</t>
+          <t>0,55; 5,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,69</t>
+          <t>0,78; 5,37</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2,71%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,01</t>
+          <t>3,35; 13,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,61</t>
+          <t>0,66; 12,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,82; 7,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 14,68</t>
+          <t>0,72; 7,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 12,92</t>
+          <t>0,0; 8,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,48</t>
+          <t>0,4; 3,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 9,05</t>
+          <t>2,7; 9,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,25</t>
+          <t>1,0; 7,11</t>
         </is>
       </c>
     </row>
@@ -1065,27 +1065,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,49%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,46%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,28</t>
+          <t>1,42; 13,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,27 +1133,27 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,28</t>
+          <t>1,62; 14,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,29</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 9,98</t>
+          <t>1,81; 9,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1180,34 +1180,34 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>26,45%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>26,04%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>26,45%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>26,25%</t>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,06; 36,89</t>
+          <t>16,55; 36,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 12,03</t>
+          <t>0,0; 6,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,08; 37,31</t>
+          <t>17,57; 36,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,96</t>
+          <t>1,25; 10,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,69; 33,58</t>
+          <t>20,23; 35,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,15</t>
+          <t>0,64; 5,74</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16,64%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>38,59%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,62%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>19,37%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>34,73%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,33</t>
+          <t>1,08; 6,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,72; 25,43</t>
+          <t>11,84; 22,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,23; 42,83</t>
+          <t>30,75; 46,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,99</t>
+          <t>0,46; 4,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,04; 21,97</t>
+          <t>14,29; 25,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,14; 50,77</t>
+          <t>28,48; 43,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,04</t>
+          <t>1,12; 4,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,3; 22,18</t>
+          <t>14,31; 21,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,22; 44,85</t>
+          <t>32,23; 42,87</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>2,05%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,08</t>
+          <t>0,36; 3,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,37; 3,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,08</t>
+          <t>0,39; 4,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,32</t>
+          <t>0,74; 4,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,26</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,49</t>
+          <t>1,04; 5,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,13</t>
+          <t>0,79; 3,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,94</t>
+          <t>0,2; 1,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,26</t>
+          <t>0,96; 3,85</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>13,14%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,36</t>
+          <t>2,96; 5,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,36; 15,13</t>
+          <t>12,81; 17,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,8; 16,81</t>
+          <t>10,48; 15,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,59</t>
+          <t>3,01; 5,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,99; 17,36</t>
+          <t>11,14; 15,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,3; 16,88</t>
+          <t>10,2; 14,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,22; 4,98</t>
+          <t>3,28; 5,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,6; 15,78</t>
+          <t>12,53; 15,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,83; 16,04</t>
+          <t>10,79; 14,0</t>
         </is>
       </c>
     </row>
@@ -1654,20 +1654,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de calefacción en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13027</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33408</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13931</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>9164</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>22896</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>31615</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>13027</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>33408</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>51411</t>
+          <t>31925</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5371; 13814</t>
+          <t>7741; 19308</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17293; 29836</t>
+          <t>26728; 39802</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23126; 43138</t>
+          <t>9430; 19569</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8349; 19745</t>
+          <t>5413; 14395</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27380; 40269</t>
+          <t>17517; 29541</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13362; 28102</t>
+          <t>12965; 24005</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15617; 29931</t>
+          <t>15766; 30444</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47715; 64796</t>
+          <t>47593; 64909</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39382; 66996</t>
+          <t>24491; 39561</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8260</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30568</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12335</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>8906</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>23095</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6469</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8260</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30568</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>18178</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4891; 15181</t>
+          <t>4440; 14693</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17118; 30953</t>
+          <t>23721; 38424</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2334; 12989</t>
+          <t>6964; 20082</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4307; 13740</t>
+          <t>4565; 15609</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23377; 37771</t>
+          <t>16920; 30287</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7610; 21425</t>
+          <t>2852; 11060</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10920; 25144</t>
+          <t>10683; 24891</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44020; 64427</t>
+          <t>44907; 64921</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11962; 30115</t>
+          <t>11878; 26832</t>
         </is>
       </c>
     </row>
@@ -2086,27 +2086,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1462</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>731</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2289</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2702</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3641</t>
+          <t>0; 4064</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>686; 6452</t>
+          <t>0; 3370</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4849</t>
+          <t>310; 4310</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3218</t>
+          <t>0; 3945</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3354</t>
+          <t>693; 6335</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>376; 5007</t>
+          <t>0; 4362</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5064</t>
+          <t>0; 5041</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>767; 7111</t>
+          <t>753; 7604</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1142; 7136</t>
+          <t>908; 6220</t>
         </is>
       </c>
     </row>
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6041</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2105</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1947</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1615</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6041</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4202</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>619; 5765</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>554; 5334</t>
+          <t>2718; 11191</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6646</t>
+          <t>476; 8697</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>639; 5965</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2481; 11914</t>
+          <t>546; 5662</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>551; 10093</t>
+          <t>0; 5926</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>631; 5562</t>
+          <t>634; 5718</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4020; 14239</t>
+          <t>4247; 14242</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1493; 10677</t>
+          <t>1414; 10089</t>
         </is>
       </c>
     </row>
@@ -2412,22 +2412,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2460,27 +2460,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2246</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>2412</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>597</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2246</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2513,12 +2513,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>711; 6268</t>
+          <t>666; 6361</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3035</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2528,27 +2528,27 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>684; 6208</t>
+          <t>711; 6450</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>0; 2977</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1627; 9051</t>
+          <t>1645; 8926</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2979</t>
+          <t>0; 2920</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2575,27 +2575,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2628,34 +2628,34 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>15275</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>14132</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>15275</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>29406</t>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2392</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9802; 20023</t>
+          <t>9554; 20807</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>505; 5556</t>
+          <t>0; 3134</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9863; 21543</t>
+          <t>9535; 19995</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4471</t>
+          <t>573; 4794</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22057; 37608</t>
+          <t>22664; 39280</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>562; 5275</t>
+          <t>604; 5439</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>4184</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>23280</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>54185</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>2250</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>26465</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>43241</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4184</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>23280</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64706</t>
+          <t>44308</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>107947</t>
+          <t>98493</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>651; 6005</t>
+          <t>1576; 8980</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20115; 34732</t>
+          <t>16567; 31559</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35147; 53322</t>
+          <t>43175; 64691</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1899; 8732</t>
+          <t>644; 5686</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16850; 30736</t>
+          <t>19522; 34985</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49832; 78732</t>
+          <t>34899; 53389</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3273; 11490</t>
+          <t>3181; 11969</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>39540; 61324</t>
+          <t>39573; 60470</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>92867; 125380</t>
+          <t>84733; 112711</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>3355</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>3662</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2105</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>6348</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1223; 8325</t>
+          <t>624; 5478</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2848</t>
+          <t>630; 5523</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1525; 8008</t>
+          <t>614; 6965</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>623; 5695</t>
+          <t>1219; 7426</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>625; 5540</t>
+          <t>0; 2955</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>724; 7013</t>
+          <t>1467; 8403</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2637; 10504</t>
+          <t>2637; 10787</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>728; 6486</t>
+          <t>674; 6446</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3170; 12251</t>
+          <t>2873; 11524</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>117</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>30537</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>111264</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>87640</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>28922</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>91985</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>89694</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>30537</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>111264</t>
-        </is>
-      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>105554</t>
+          <t>76600</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>195248</t>
+          <t>164240</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>20748; 37967</t>
+          <t>22281; 41389</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>79563; 105936</t>
+          <t>94773; 129732</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71831; 111837</t>
+          <t>73275; 105461</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22184; 42082</t>
+          <t>21305; 39198</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>96101; 128502</t>
+          <t>78028; 106883</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>85913; 128326</t>
+          <t>64089; 90782</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47059; 72732</t>
+          <t>47920; 73045</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>181435; 227202</t>
+          <t>180428; 225587</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>168616; 228630</t>
+          <t>143231; 185929</t>
         </is>
       </c>
     </row>
